--- a/exports/COFORGE_full_report.xlsx
+++ b/exports/COFORGE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:U74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1084</v>
+        <v>1059</v>
       </c>
       <c r="I2" t="n">
         <v>1080.471163</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.13</v>
+        <v>-5.36</v>
       </c>
       <c r="L2" t="n">
-        <v>3.75</v>
+        <v>5.59</v>
       </c>
       <c r="M2" t="n">
         <v>1.31</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>898</v>
+        <v>930</v>
       </c>
       <c r="I3" t="n">
         <v>919.0703180544766</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>15.2</v>
+        <v>12.18</v>
       </c>
       <c r="L3" t="n">
         <v>3.12</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>916.5</v>
+        <v>855</v>
       </c>
       <c r="I4" t="n">
         <v>888.5361623376647</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.45</v>
+        <v>-8.06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.55</v>
+        <v>8.66</v>
       </c>
       <c r="M4" t="n">
-        <v>3.32</v>
+        <v>5.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.98</v>
+        <v>7.69</v>
       </c>
       <c r="O4" t="n">
         <v>3.9</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>735</v>
+        <v>778</v>
       </c>
       <c r="I5" t="n">
         <v>764.8022121031391</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>81</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04</v>
+        <v>9.01</v>
       </c>
       <c r="L5" t="n">
         <v>7.72</v>
@@ -726,7 +785,7 @@
         <v>3.02</v>
       </c>
       <c r="N5" t="n">
-        <v>6.06</v>
+        <v>6.53</v>
       </c>
       <c r="O5" t="n">
         <v>-7.69</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>12.23</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44719.38541666666</v>
+        <v>44719.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>715</v>
+        <v>707.5</v>
       </c>
       <c r="I6" t="n">
         <v>709.8285146629261</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.1</v>
+        <v>-9.06</v>
       </c>
       <c r="L6" t="n">
-        <v>8.869999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44732.55208333334</v>
+        <v>44733.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>674</v>
+        <v>710.5</v>
       </c>
       <c r="I7" t="n">
         <v>706.5081385952362</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>4.73</v>
+        <v>-0.42</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -840,7 +923,7 @@
         <v>2.33</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>6.45</v>
       </c>
       <c r="O7" t="n">
         <v>-2.08</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44742.55208333334</v>
+        <v>44743.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>707.5</v>
+        <v>692</v>
       </c>
       <c r="I8" t="n">
         <v>697.3698948013235</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.42</v>
+        <v>-2.6</v>
       </c>
       <c r="L8" t="n">
         <v>4.36</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44762.55208333334</v>
+        <v>44763.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>708.5</v>
+        <v>723.5</v>
       </c>
       <c r="I9" t="n">
         <v>723.3257462106719</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.38</v>
+        <v>-4.55</v>
       </c>
       <c r="L9" t="n">
-        <v>7.51</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
         <v>1.8</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>7.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>752</v>
+        <v>739.5</v>
       </c>
       <c r="I10" t="n">
         <v>749.7038504096787</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>3.94</v>
+        <v>2.21</v>
       </c>
       <c r="L10" t="n">
         <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>2.66</v>
       </c>
       <c r="N10" t="n">
         <v>3.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>6.51</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44830.55208333334</v>
+        <v>44831.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>676.5</v>
+        <v>693</v>
       </c>
       <c r="I11" t="n">
         <v>688.2465549727236</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>8.52</v>
+        <v>6.29</v>
       </c>
       <c r="L11" t="n">
         <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="N11" t="n">
         <v>2.85</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="I12" t="n">
         <v>757.9850770590317</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K12" t="n">
-        <v>10.1</v>
+        <v>8.66</v>
       </c>
       <c r="L12" t="n">
         <v>4.91</v>
       </c>
       <c r="M12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="N12" t="n">
         <v>3.86</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.47</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="I13" t="n">
         <v>798.6733588798285</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.58</v>
+        <v>-6.11</v>
       </c>
       <c r="L13" t="n">
-        <v>5.98</v>
+        <v>6.51</v>
       </c>
       <c r="M13" t="n">
         <v>0.26</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.59</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44902.38541666666</v>
+        <v>44902.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>805.5</v>
+        <v>803</v>
       </c>
       <c r="I14" t="n">
         <v>803.686159886047</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="I15" t="n">
         <v>795.0968527863552</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>1.87</v>
+        <v>0.12</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.25</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44967.55208333334</v>
+        <v>44970.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>869.5</v>
+        <v>810.5</v>
       </c>
       <c r="I16" t="n">
         <v>827.3535617279451</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>8.42</v>
+        <v>1.06</v>
       </c>
       <c r="L16" t="n">
         <v>5.49</v>
       </c>
       <c r="M16" t="n">
-        <v>0.95</v>
+        <v>6.84</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>7.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.71</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.48</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44977.38541666666</v>
+        <v>44977.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="I17" t="n">
         <v>865.6652992341009</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.98</v>
+        <v>-7.09</v>
       </c>
       <c r="L17" t="n">
-        <v>6.23</v>
+        <v>7.71</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>850</v>
+        <v>828</v>
       </c>
       <c r="I18" t="n">
         <v>838.458895227692</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.07</v>
+        <v>-4.61</v>
       </c>
       <c r="L18" t="n">
-        <v>4.26</v>
+        <v>5.13</v>
       </c>
       <c r="M18" t="n">
         <v>1.21</v>
       </c>
       <c r="N18" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
         <v>3.33</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="I19" t="n">
         <v>762.5582048882806</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>8.09</v>
+        <v>7.25</v>
       </c>
       <c r="L19" t="n">
         <v>2.42</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.98</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>804.5</v>
+        <v>765</v>
       </c>
       <c r="I20" t="n">
         <v>769.7484725650221</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>4.75</v>
+        <v>-0.39</v>
       </c>
       <c r="L20" t="n">
-        <v>0.98</v>
+        <v>2.28</v>
       </c>
       <c r="M20" t="n">
-        <v>0.49</v>
+        <v>3.36</v>
       </c>
       <c r="N20" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="O20" t="n">
         <v>0.92</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>7.32</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="I21" t="n">
         <v>820.3588298146534</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.14</v>
+        <v>-9.02</v>
       </c>
       <c r="L21" t="n">
-        <v>6.54</v>
+        <v>10.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="N21" t="n">
         <v>3.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.11</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45084.55208333334</v>
+        <v>45085.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="I22" t="n">
         <v>879.0161445445174</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>6.71</v>
+        <v>5.4</v>
       </c>
       <c r="L22" t="n">
         <v>2.76</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.26</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>913.5</v>
+        <v>922.5</v>
       </c>
       <c r="I23" t="n">
         <v>915.9884638771172</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.92</v>
+        <v>-4.95</v>
       </c>
       <c r="L23" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="M23" t="n">
         <v>0.78</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45127.55208333334</v>
+        <v>45128.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>953.5</v>
+        <v>939</v>
       </c>
       <c r="I24" t="n">
         <v>942.1618530569981</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
-        <v>3.36</v>
+        <v>1.79</v>
       </c>
       <c r="L24" t="n">
         <v>4.77</v>
@@ -1809,7 +2096,7 @@
         <v>0.89</v>
       </c>
       <c r="N24" t="n">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
         <v>1.26</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="I25" t="n">
         <v>976.8607140390097</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.94</v>
+        <v>-5.32</v>
       </c>
       <c r="L25" t="n">
-        <v>4.69</v>
+        <v>5.59</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45154.55208333334</v>
+        <v>45155.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="I26" t="n">
         <v>1009.789382407691</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>3.13</v>
+        <v>1.62</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>6.94</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>979</v>
+        <v>1067.5</v>
       </c>
       <c r="I27" t="n">
         <v>1031.483048667066</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.59</v>
+        <v>-6.22</v>
       </c>
       <c r="L27" t="n">
-        <v>2.04</v>
+        <v>7.06</v>
       </c>
       <c r="M27" t="n">
         <v>0.85</v>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>9.81</v>
       </c>
       <c r="O27" t="n">
         <v>-1.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1084</v>
+        <v>1066</v>
       </c>
       <c r="I28" t="n">
         <v>1072.573009912785</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>1.55</v>
+        <v>-0.14</v>
       </c>
       <c r="L28" t="n">
         <v>11.9</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.37</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="I29" t="n">
         <v>1024.976403606841</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>4.13</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>1.45</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.19</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1208</v>
+        <v>1189</v>
       </c>
       <c r="I30" t="n">
         <v>1203.356932675983</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>17.85</v>
+        <v>16</v>
       </c>
       <c r="L30" t="n">
         <v>1.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.64</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="I31" t="n">
         <v>1250.137244693143</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.45</v>
+        <v>-5.55</v>
       </c>
       <c r="L31" t="n">
-        <v>5.55</v>
+        <v>6.64</v>
       </c>
       <c r="M31" t="n">
         <v>2.23</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5.6</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="I32" t="n">
         <v>1253.003262363511</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>0.84</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.59</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.5</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45328.38541666666</v>
+        <v>45328.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="I33" t="n">
         <v>1308.178502912532</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.41</v>
+        <v>-4.97</v>
       </c>
       <c r="L33" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="M33" t="n">
         <v>1.55</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.99</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1288</v>
+        <v>1265</v>
       </c>
       <c r="I34" t="n">
         <v>1272.282114280293</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.68</v>
+        <v>-3.44</v>
       </c>
       <c r="L34" t="n">
-        <v>2.44</v>
+        <v>3.82</v>
       </c>
       <c r="M34" t="n">
         <v>1.73</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>6.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45385.55208333334</v>
+        <v>45386.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1133</v>
+        <v>1163</v>
       </c>
       <c r="I35" t="n">
         <v>1153.983578031728</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>10.43</v>
+        <v>8.06</v>
       </c>
       <c r="L35" t="n">
         <v>1.9</v>
       </c>
       <c r="M35" t="n">
-        <v>1.73</v>
+        <v>3.09</v>
       </c>
       <c r="N35" t="n">
         <v>2.89</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>5.28</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1122</v>
+        <v>1089</v>
       </c>
       <c r="I36" t="n">
         <v>1106.03495955724</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.53</v>
+        <v>-6.36</v>
       </c>
       <c r="L36" t="n">
-        <v>3.7</v>
+        <v>6.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0.13</v>
+        <v>1.69</v>
       </c>
       <c r="N36" t="n">
-        <v>1.73</v>
+        <v>3.97</v>
       </c>
       <c r="O36" t="n">
         <v>2.69</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.16</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45428.38541666666</v>
+        <v>45428.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="I37" t="n">
         <v>924.7532508568086</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>15.15</v>
+        <v>14.14</v>
       </c>
       <c r="L37" t="n">
         <v>2.57</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.29</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1000</v>
+        <v>992.5</v>
       </c>
       <c r="I38" t="n">
         <v>997.2860203662409</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>6.95</v>
+        <v>6.15</v>
       </c>
       <c r="L38" t="n">
         <v>1.82</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45449.38541666666</v>
+        <v>45449.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1038</v>
+        <v>1047</v>
       </c>
       <c r="I39" t="n">
         <v>1044.999614450941</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.58</v>
+        <v>-5.49</v>
       </c>
       <c r="L39" t="n">
         <v>6.25</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.53</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45484.38541666666</v>
+        <v>45484.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="I40" t="n">
         <v>1115.229514440299</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K40" t="n">
-        <v>6.69</v>
+        <v>6.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.38</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.77</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1113</v>
+        <v>1185.5</v>
       </c>
       <c r="I41" t="n">
         <v>1177.252106227807</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>-6.51</v>
       </c>
       <c r="L41" t="n">
-        <v>0.45</v>
+        <v>7.37</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="O41" t="n">
         <v>-1.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1216.5</v>
+        <v>1167</v>
       </c>
       <c r="I42" t="n">
         <v>1196.372755957818</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>2.61</v>
+        <v>-1.56</v>
       </c>
       <c r="L42" t="n">
         <v>4.98</v>
       </c>
       <c r="M42" t="n">
-        <v>1.74</v>
+        <v>4.64</v>
       </c>
       <c r="N42" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="O42" t="n">
         <v>7.23</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.98</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45531.55208333334</v>
+        <v>45532.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1215</v>
+        <v>1258</v>
       </c>
       <c r="I43" t="n">
         <v>1232.158318351541</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.11</v>
+        <v>-7.8</v>
       </c>
       <c r="L43" t="n">
-        <v>6.43</v>
+        <v>8.74</v>
       </c>
       <c r="M43" t="n">
         <v>2.05</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.27</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45583.55208333334</v>
+        <v>45586.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1444</v>
+        <v>1371.5</v>
       </c>
       <c r="I44" t="n">
         <v>1425.61830547159</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K44" t="n">
-        <v>14.79</v>
+        <v>9.02</v>
       </c>
       <c r="L44" t="n">
         <v>3.34</v>
@@ -2949,7 +3476,7 @@
         <v>2.46</v>
       </c>
       <c r="N44" t="n">
-        <v>3.32</v>
+        <v>5.68</v>
       </c>
       <c r="O44" t="n">
         <v>2.72</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.16</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45587.55208333334</v>
+        <v>45588.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1361.5</v>
+        <v>1506.5</v>
       </c>
       <c r="I45" t="n">
         <v>1445.606339817212</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>0.73</v>
+        <v>-9.84</v>
       </c>
       <c r="L45" t="n">
-        <v>5.54</v>
+        <v>11.52</v>
       </c>
       <c r="M45" t="n">
-        <v>0.29</v>
+        <v>2.09</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>10.98</v>
       </c>
       <c r="O45" t="n">
         <v>-5.68</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.86</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1890</v>
+        <v>1769.5</v>
       </c>
       <c r="I46" t="n">
         <v>1851.18103771497</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K46" t="n">
-        <v>25.46</v>
+        <v>17.46</v>
       </c>
       <c r="L46" t="n">
         <v>7.93</v>
@@ -3063,7 +3614,7 @@
         <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>3.1</v>
+        <v>7.46</v>
       </c>
       <c r="O46" t="n">
         <v>10.98</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1644.5</v>
+        <v>1852</v>
       </c>
       <c r="I47" t="n">
         <v>1760.528708943192</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>7.06</v>
+        <v>-4.66</v>
       </c>
       <c r="L47" t="n">
         <v>5.37</v>
       </c>
       <c r="M47" t="n">
-        <v>0.42</v>
+        <v>5.93</v>
       </c>
       <c r="N47" t="n">
-        <v>1.54</v>
+        <v>11.58</v>
       </c>
       <c r="O47" t="n">
         <v>-7.46</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>12.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1698</v>
+        <v>1665.5</v>
       </c>
       <c r="I48" t="n">
         <v>1697.141214062372</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.32</v>
+        <v>-10.07</v>
       </c>
       <c r="L48" t="n">
-        <v>9.23</v>
+        <v>10.37</v>
       </c>
       <c r="M48" t="n">
         <v>1.46</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.11</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1443</v>
+        <v>1565</v>
       </c>
       <c r="I49" t="n">
         <v>1559.778623531618</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>13.36</v>
+        <v>6.03</v>
       </c>
       <c r="L49" t="n">
         <v>3.57</v>
       </c>
       <c r="M49" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>-4.83</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>10.71</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1554</v>
+        <v>1434.5</v>
       </c>
       <c r="I50" t="n">
         <v>1528.526597779169</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.7</v>
+        <v>-8.34</v>
       </c>
       <c r="L50" t="n">
-        <v>7.99</v>
+        <v>8.5</v>
       </c>
       <c r="M50" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.72</v>
+        <v>7.92</v>
       </c>
       <c r="O50" t="n">
         <v>8.390000000000001</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>12.26</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1331</v>
+        <v>1401</v>
       </c>
       <c r="I51" t="n">
         <v>1389.160363103209</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>7.22</v>
+        <v>2.34</v>
       </c>
       <c r="L51" t="n">
         <v>6.66</v>
@@ -3348,7 +3959,7 @@
         <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>4.11</v>
+        <v>4.28</v>
       </c>
       <c r="O51" t="n">
         <v>-7.92</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>12.15</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1887.5</v>
+        <v>1858.5</v>
       </c>
       <c r="I52" t="n">
         <v>1878.03931379191</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>80.16666666666667</v>
+        <v>81</v>
       </c>
       <c r="K52" t="n">
-        <v>34.73</v>
+        <v>32.66</v>
       </c>
       <c r="L52" t="n">
         <v>4.85</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.78</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1658</v>
+        <v>1719.8</v>
       </c>
       <c r="I53" t="n">
         <v>1717.744920575724</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K53" t="n">
-        <v>10.79</v>
+        <v>7.46</v>
       </c>
       <c r="L53" t="n">
         <v>3.04</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1692</v>
+        <v>1664.8</v>
       </c>
       <c r="I54" t="n">
         <v>1684.381152566126</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.62</v>
+        <v>-3.2</v>
       </c>
       <c r="L54" t="n">
         <v>5.06</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.56</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1697</v>
+        <v>1769.8</v>
       </c>
       <c r="I55" t="n">
         <v>1758.875300112098</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.93</v>
+        <v>-6.31</v>
       </c>
       <c r="L55" t="n">
-        <v>2.96</v>
+        <v>6.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="N55" t="n">
-        <v>2.11</v>
+        <v>4.24</v>
       </c>
       <c r="O55" t="n">
         <v>-1.83</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.47</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1799</v>
+        <v>1727.3</v>
       </c>
       <c r="I56" t="n">
         <v>1741.49982513436</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>1.65</v>
+        <v>-2.4</v>
       </c>
       <c r="L56" t="n">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="M56" t="n">
-        <v>0.18</v>
+        <v>4.39</v>
       </c>
       <c r="N56" t="n">
-        <v>1.52</v>
+        <v>4.65</v>
       </c>
       <c r="O56" t="n">
         <v>4.24</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.54</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1614.9</v>
+        <v>1646.8</v>
       </c>
       <c r="I57" t="n">
         <v>1639.012887197616</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
-        <v>6.51</v>
+        <v>4.66</v>
       </c>
       <c r="L57" t="n">
         <v>1.12</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.44</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45999.55208333334</v>
+        <v>46000.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1948</v>
+        <v>1873.1</v>
       </c>
       <c r="I58" t="n">
         <v>1893.149030080156</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K58" t="n">
-        <v>18.29</v>
+        <v>13.74</v>
       </c>
       <c r="L58" t="n">
         <v>2.96</v>
@@ -3747,7 +4442,7 @@
         <v>0.75</v>
       </c>
       <c r="N58" t="n">
-        <v>2.93</v>
+        <v>3.95</v>
       </c>
       <c r="O58" t="n">
         <v>2.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.98</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46038.38541666666</v>
+        <v>46038.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1722.6</v>
+        <v>1732</v>
       </c>
       <c r="I59" t="n">
         <v>1726.785214604428</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>8.029999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="L59" t="n">
         <v>3.47</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>5.24</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46042.55208333334</v>
+        <v>46043.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1695</v>
+        <v>1647.5</v>
       </c>
       <c r="I60" t="n">
         <v>1648.097502601304</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.14</v>
+        <v>-4.88</v>
       </c>
       <c r="L60" t="n">
-        <v>2.66</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>-0</v>
+        <v>0.08</v>
       </c>
       <c r="N60" t="n">
         <v>1.79</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.02</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1111.9</v>
+        <v>1154.1</v>
       </c>
       <c r="I61" t="n">
         <v>1153.120651143007</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K61" t="n">
-        <v>32.51</v>
+        <v>29.95</v>
       </c>
       <c r="L61" t="n">
         <v>6.77</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.26</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46133.55208333334</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1294.4</v>
+        <v>1222</v>
       </c>
       <c r="I62" t="n">
         <v>1225.245272977225</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K62" t="n">
-        <v>12.16</v>
+        <v>5.88</v>
       </c>
       <c r="L62" t="n">
         <v>3.8</v>
@@ -3975,7 +4718,7 @@
         <v>1.85</v>
       </c>
       <c r="N62" t="n">
-        <v>3.09</v>
+        <v>4.38</v>
       </c>
       <c r="O62" t="n">
         <v>4.51</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1168</v>
+        <v>1275.5</v>
       </c>
       <c r="I63" t="n">
         <v>1236.387217680621</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>4.42</v>
+        <v>-4.38</v>
       </c>
       <c r="L63" t="n">
-        <v>4.25</v>
+        <v>6.04</v>
       </c>
       <c r="M63" t="n">
-        <v>1.23</v>
+        <v>7.98</v>
       </c>
       <c r="N63" t="n">
-        <v>4.26</v>
+        <v>9.59</v>
       </c>
       <c r="O63" t="n">
         <v>-4.38</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.93</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1295.5</v>
+        <v>1266.6</v>
       </c>
       <c r="I64" t="n">
         <v>1278.438939506797</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>1.57</v>
+        <v>-0.7</v>
       </c>
       <c r="L64" t="n">
         <v>2.24</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>9</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1348.1</v>
+        <v>1427.3</v>
       </c>
       <c r="I65" t="n">
         <v>1366.795597299568</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.43</v>
+        <v>-12.69</v>
       </c>
       <c r="L65" t="n">
-        <v>6.73</v>
+        <v>14.24</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="N65" t="n">
         <v>5.68</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.12</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1400.8</v>
+        <v>1395.7</v>
       </c>
       <c r="I66" t="n">
         <v>1396.552428671055</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.86</v>
+        <v>-2.21</v>
       </c>
       <c r="L66" t="n">
-        <v>4.69</v>
+        <v>4.98</v>
       </c>
       <c r="M66" t="n">
         <v>1.47</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.51</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>1461.3</v>
+        <v>1468</v>
       </c>
       <c r="I67" t="n">
         <v>1467.516346953124</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.7</v>
+        <v>-5.18</v>
       </c>
       <c r="L67" t="n">
         <v>7.32</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.49</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1470</v>
+        <v>1409.6</v>
       </c>
       <c r="I68" t="n">
         <v>1418.678003027592</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>0.14</v>
+        <v>-3.98</v>
       </c>
       <c r="L68" t="n">
         <v>4.78</v>
@@ -4317,7 +5132,7 @@
         <v>5.18</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>6.94</v>
       </c>
       <c r="O68" t="n">
         <v>0.07000000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1483</v>
+        <v>1507.6</v>
       </c>
       <c r="I69" t="n">
         <v>1491.329990992238</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.21</v>
+        <v>-6.95</v>
       </c>
       <c r="L69" t="n">
-        <v>5.9</v>
+        <v>7.26</v>
       </c>
       <c r="M69" t="n">
         <v>1.97</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.46</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1471</v>
+        <v>1441</v>
       </c>
       <c r="I70" t="n">
         <v>1448.716147150257</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.43</v>
+        <v>-4.42</v>
       </c>
       <c r="L70" t="n">
         <v>5.29</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.81</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46230.38541666666</v>
+        <v>46230.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>1524.3</v>
+        <v>1531</v>
       </c>
       <c r="I71" t="n">
         <v>1525.611844472052</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>-5.78</v>
+        <v>-6.25</v>
       </c>
       <c r="L71" t="n">
-        <v>6.46</v>
+        <v>6.75</v>
       </c>
       <c r="M71" t="n">
         <v>0.64</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>5.73</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1941</v>
+        <v>1857.4</v>
       </c>
       <c r="I72" t="n">
         <v>1911.706667414134</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K72" t="n">
-        <v>26.78</v>
+        <v>21.32</v>
       </c>
       <c r="L72" t="n">
         <v>0.58</v>
       </c>
       <c r="M72" t="n">
-        <v>1.78</v>
+        <v>6.47</v>
       </c>
       <c r="N72" t="n">
-        <v>1.81</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>3.03</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>5.07</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1816</v>
+        <v>1856.5</v>
       </c>
       <c r="I73" t="n">
         <v>1852.63770904983</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K73" t="n">
-        <v>2.23</v>
+        <v>0.05</v>
       </c>
       <c r="L73" t="n">
         <v>1.95</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4662,6 +5549,12 @@
       <c r="Q74" t="n">
         <v>24</v>
       </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6764,7 +7657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="6">
@@ -6774,7 +7667,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7">
@@ -6784,7 +7677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -6794,7 +7687,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -6804,7 +7697,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.3</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="10">
@@ -6814,7 +7707,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.6</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="11">
@@ -6854,7 +7747,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="15">
@@ -6864,7 +7757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.87</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="16">
@@ -6874,7 +7767,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.03</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="17">
@@ -6884,7 +7777,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.73</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="18">
@@ -6894,7 +7787,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="19">
@@ -6904,7 +7797,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.19</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="20">
@@ -6914,7 +7807,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.98</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="21">
@@ -6924,7 +7817,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.9</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="22">
@@ -6934,7 +7827,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6944,7 +7837,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -6954,7 +7847,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="25">
@@ -6964,7 +7857,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.18</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="26">
@@ -6974,7 +7867,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.17</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="27">
@@ -6984,7 +7877,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.86</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="28">
@@ -6994,7 +7887,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
